--- a/data_output/metab_combined_volcano.xlsx
+++ b/data_output/metab_combined_volcano.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H459"/>
+  <dimension ref="A1:I459"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -395,6 +395,11 @@
           <t>source</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>compound_unique</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -427,6 +432,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>(carbomethoxymethylene)-triphenylphosphorane</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -459,6 +469,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1,2,4-benzenetriol</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -491,6 +506,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1,6-anhydro-glucose</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -523,6 +543,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1,6-diisopropylnaphthalene</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -555,6 +580,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1,7-bis(3,4-dihydroxyphenyl)-6-hydroxyheptan-3-one</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -587,6 +617,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1-(2-hydroxyethylamino)-2-propanol</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -619,6 +654,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1-kestose</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -651,6 +691,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1-methyladenosine</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -683,6 +728,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1-methylguanidine</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -715,6 +765,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1-monopalmitin</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -747,6 +802,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1-octanesulfonic acid</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -779,6 +839,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>12,13-DiHOME</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -811,6 +876,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>12-hydroxy-4-methyl-octahydro-3-benzoxecine-2,9-dione</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -843,6 +913,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2'-deoxy-2'-fluoro-2'-methyluridine</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -875,6 +950,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2'-deoxyadenosine</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -907,6 +987,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2'-deoxycytidine</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -939,6 +1024,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2'-deoxyguanosine</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -971,6 +1061,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2'-deoxyinosine</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1003,6 +1098,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2'-fucosyllactose</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1035,6 +1135,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2,3-diaminopropionic acid</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1067,6 +1172,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2,3-dihydroxybenzenepropanoic acid</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1099,6 +1209,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2,3-dihydroxypyridine</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1131,6 +1246,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2,4-dihydroxybutanoic acid</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1163,6 +1283,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2,4-dinitrophenol</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1195,6 +1320,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2,4-hexadienedioic acid</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1227,6 +1357,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2,6-diaminopimelic acid</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1259,6 +1394,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2-(5-methylpyrazol-1-yl)propanoic acid</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1291,6 +1431,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2-Deoxyinosine</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1323,6 +1468,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2-amino-5-methoxyphenol</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1355,6 +1505,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2-benzothiazolesulfonic acid</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1387,6 +1542,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2-deoxyadenosine</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1419,6 +1579,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2-deoxyerythritol</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1451,6 +1616,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2-deoxytetronic acid</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1483,6 +1653,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2-hydroxy-5-methylbenzoic acid</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1515,6 +1690,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2-hydroxybenzoic acid-6-pentadecatriene</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1547,6 +1727,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2-hydroxybutanoic acid</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1579,6 +1764,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2-hydroxyglutaric acid</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1611,6 +1801,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2-hydroxyisocaproic acid</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1643,6 +1838,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2-hydroxyisovaleric acid</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1675,6 +1875,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2-hydroxyoctanoic acid</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1707,6 +1912,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2-hydroxyphenethylamine</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1739,6 +1949,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2-hydroxyvaleric acid</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1771,6 +1986,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2-isopropylmalic acid</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1803,6 +2023,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2-keto-3-deoxygluconic acid</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1835,6 +2060,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2-ketoadipic acid</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1867,6 +2097,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2-ketobutyric acid</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1899,6 +2134,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2-ketoisocaproic acid</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1931,6 +2171,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2-ketoisovaleric acid</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1963,6 +2208,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2-ketomethionine</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1995,6 +2245,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2-methoxyphenol sulfate</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2027,6 +2282,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2-methyl-1-pyrroline</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2059,6 +2319,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2-methylglyceric acid</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2091,6 +2356,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2-oct-7-enylpentanedioic acid</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2123,6 +2393,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2-oxindole-3-acetate</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2155,6 +2430,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2-picolinic acid</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2187,6 +2467,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2-pyrrolidinone</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2219,6 +2504,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>3,4-dihydroxybenzoic acid</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2251,6 +2541,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>3,4-dihydroxycinnamic acid</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2283,6 +2578,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>3,6-anhydro-D-galactose</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2315,6 +2615,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>3,8-dihydroxy-8-(hydroxymethyl)-4,4,11b-trimethyldodecahydro-6a,9-methanocyclohepta[a]naphthalene-2,6-dione</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2347,6 +2652,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>3-(3-hydroxyphenyl)-3-hydroxypropionic acid</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2379,6 +2689,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>3-(3-hydroxyphenyl)propionic acid</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2411,6 +2726,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>3-(4-hydroxyphenyl)propionic acid</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2443,6 +2763,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>3-acetyl-5-methyloxolan-2-one</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2475,6 +2800,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>3-amino-1-propanol</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2507,6 +2837,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>3-aminoisobutyric acid</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2539,6 +2874,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>3-dehydroshikimic acid</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2571,6 +2911,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>3-dehydroxy-carnitine</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2603,6 +2948,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>3-deoxy-glycero-galacto-2-nonulosonic acid</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2635,6 +2985,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>3-deoxyguanosine</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2667,6 +3022,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>3-furancarboxylic acid, tetrahydro-4-methylene-2-octyl-5-oxo-</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2699,6 +3059,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>3-hydroxy-1-propanesulfonic acid</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2731,6 +3096,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>3-hydroxy-3-methylglutaric acid</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2763,6 +3133,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>3-hydroxyacetophenone</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2795,6 +3170,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>3-hydroxybenzoic acid</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2827,6 +3207,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>3-hydroxybutyric acid</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2859,6 +3244,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>3-hydroxyphenylacetic acid</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2891,6 +3281,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>3-hydroxypropionic acid</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2923,6 +3318,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>3-hydroxysebacic acid</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2955,6 +3355,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>3-isopropylmalic acid</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2987,6 +3392,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>3-methyladipic acid</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3019,6 +3429,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>3-methylglutaric acid</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3051,6 +3466,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>3-oxodeoxycholic acid</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3083,6 +3503,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>3-pyridylacetic acid</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3115,6 +3540,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>4,4'-sulfonyl-bis(2-allylphenol)</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3147,6 +3577,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>4-acetamido-butanoic acid</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3179,6 +3614,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>4-hydroxy-2,6-tetramethyl-1-piperidine ethanol</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3211,6 +3651,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>4-hydroxybenzaldehyde</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3243,6 +3688,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>4-hydroxybenzoic acid</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3275,6 +3725,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>4-hydroxybutyric acid</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3307,6 +3762,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>4-hydroxycinnamic acid</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3339,6 +3799,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>4-hydroxyphenylacetic acid</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3371,6 +3836,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>4-hydroxyquinoline</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3403,6 +3873,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>4-methylcatechol</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3435,6 +3910,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>4-oxododecanedioic acid</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3467,6 +3947,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>5-aminovaleric acid</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3499,6 +3984,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>5-hydroxyectoine</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3531,6 +4021,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>5-hydroxymethyl-2-furoic acid</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3563,6 +4058,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>5-methoxysalicylic acid</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3595,6 +4095,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>5-methylcytosine</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3627,6 +4132,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>6-hydroxynicotinic acid</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3659,6 +4169,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>9-(2,3-dihydroxypropoxy)-9-oxononanoic acid</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3691,6 +4206,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>9-hydroxydec-2-enoic acid</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3723,6 +4243,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Ala-Asp</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3755,6 +4280,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Ala-Thr</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3787,6 +4317,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Asn-Val</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3819,6 +4354,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Asp Leu</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3851,6 +4391,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Asp-Val</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3883,6 +4428,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Benzaldehyde-4-carboxylic acid</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3915,6 +4465,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>D-erythro-sphingosine</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3947,6 +4502,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>DG 18:2_18:2</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3979,6 +4539,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Dopamine</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4011,6 +4576,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Gln-Asp</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4043,6 +4613,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Gln-Glu</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4075,6 +4650,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Glu-Gln</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4107,6 +4687,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Glu-Leu</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4139,6 +4724,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Gly Pro</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4171,6 +4761,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Gly-Asp</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4203,6 +4798,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Gly-Met</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4235,6 +4835,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Ile-Ala</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4267,6 +4872,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Ile-Glu</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4299,6 +4909,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Ile-Pro</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4331,6 +4946,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>L-Methionine</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4363,6 +4983,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>MOPS</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4395,6 +5020,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>N,N,N-trimethyl-5-aminovalerate</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4427,6 +5057,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>N,N-dimethyl-proline-proline betaine</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4459,6 +5094,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>N-(5-methyl-3-isoxazolyl)benzenesulfonamide</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4491,6 +5131,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>N-acetyl-D-galactosamine</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4523,6 +5168,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>N-acetyl-glucosaminitol</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4555,6 +5205,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>N-acetyl-glutamic acid</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4587,6 +5242,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>N-acetyl-lactosamine</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4619,6 +5279,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>N-acetyl-ornithine</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4651,6 +5316,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>N-acetyl-serine</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4683,6 +5353,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>N-acetyl-valine</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4715,6 +5390,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>N-acetylglutamate</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4747,6 +5427,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>N-acetylmannosamine</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4779,6 +5464,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>N-carbamoylaspartate</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4811,6 +5501,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>N-formylanthranilic acid</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4843,6 +5538,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>N-formylpiperidine</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4875,6 +5575,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>N-methylglutamic acid</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4907,6 +5612,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>N-methylproline</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4939,6 +5649,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>N6-methyl-2'-deoxyadenosine</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4971,6 +5686,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>PE 18:0_18:0</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5003,6 +5723,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>PI 38:6</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5035,6 +5760,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Phe-Glu</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5067,6 +5797,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Pro-Ile</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5099,6 +5834,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Pro-Thr</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5131,6 +5871,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Ser-Asp</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5163,6 +5908,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>TMAO</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5195,6 +5945,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Thr-Leu</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5227,6 +5982,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Traumatic Acid</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5259,6 +6019,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>UDP-N-acetylglucosamine</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5291,6 +6056,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Val Glu Leu</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5323,6 +6093,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Val-Thr</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5355,6 +6130,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>aconitic acid</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5387,6 +6167,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>acylcarnitine 02:0</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5419,6 +6204,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>acylcarnitine 03:0</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5451,6 +6241,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>acylcarnitine 04:0, branched</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5483,6 +6278,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>acylcarnitine 16:0</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5515,6 +6315,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>acylcarnitine, isovaleryl-</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5547,6 +6352,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>acylcarnitine, malonyl-</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5579,6 +6389,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>adenosine</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5611,6 +6426,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>adipic acid</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5643,6 +6463,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>alanine</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5675,6 +6500,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>alanine betaine</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5707,6 +6537,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>alanine-alanine</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5739,6 +6574,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>aleuritic acid</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5771,6 +6611,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>allantoin</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5803,6 +6648,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>alpha-aminoadipic acid</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5835,6 +6685,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>alpha-artemisic acid</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5867,6 +6722,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>alpha-ketoglutarate</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5899,6 +6759,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>anthranilic acid</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5931,6 +6796,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>arabitol</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -5963,6 +6833,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>arachidic acid</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -5995,27 +6870,32 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>aspartic acid</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>azelaic acid (GCMS)</t>
+          <t>azelaic acid</t>
         </is>
       </c>
       <c r="B177">
-        <v>1324.277777777778</v>
+        <v>13289.27777777778</v>
       </c>
       <c r="C177">
-        <v>5995.444444444444</v>
+        <v>48363.22222222222</v>
       </c>
       <c r="D177">
-        <v>0.0008192537871697544</v>
+        <v>0.004584665528140498</v>
       </c>
       <c r="E177">
-        <v>2.178660934477356</v>
+        <v>1.86364766631893</v>
       </c>
       <c r="F177">
-        <v>3.08658154232505</v>
+        <v>2.338692342563526</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
@@ -6024,30 +6904,35 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>GCMS</t>
+          <t>LCMS</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>azelaic acid (LCMS)</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>azelaic acid (LCMS)</t>
+          <t>azelaic acid</t>
         </is>
       </c>
       <c r="B178">
-        <v>13289.27777777778</v>
+        <v>1324.277777777778</v>
       </c>
       <c r="C178">
-        <v>48363.22222222222</v>
+        <v>5995.444444444444</v>
       </c>
       <c r="D178">
-        <v>0.004584665528140498</v>
+        <v>0.0008192537871697544</v>
       </c>
       <c r="E178">
-        <v>1.86364766631893</v>
+        <v>2.178660934477356</v>
       </c>
       <c r="F178">
-        <v>2.338692342563526</v>
+        <v>3.08658154232505</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
@@ -6056,7 +6941,12 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>LCMS</t>
+          <t>GCMS</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>azelaic acid (GCMS)</t>
         </is>
       </c>
     </row>
@@ -6091,6 +6981,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>behenic acid</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6123,6 +7018,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>benzenesulfonic acid, decyl-</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6155,6 +7055,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>benzoic acid</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6187,6 +7092,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>benzothiazole</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -6219,6 +7129,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>benzyltriethylammonium</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -6251,6 +7166,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>benzyltrimethylammonium</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6283,6 +7203,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>beta-alanine</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6315,6 +7240,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>beta-gentiobiose</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6347,6 +7277,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>beta-glutamic acid</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6379,6 +7314,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>beta-mannosylglycerate</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6411,6 +7351,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>beta-sitosterol</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6443,6 +7388,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>beta-sitosteryl sulfate</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6475,6 +7425,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>betaine</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6507,6 +7462,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>betaine aldehyde</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -6539,6 +7499,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>bis-ferulamidobutane</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -6571,6 +7536,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>butane-2,3-diol</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -6603,6 +7573,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>butyraldehyde</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -6635,6 +7610,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>butyrolactam</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -6667,6 +7647,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>cadaverine</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -6699,6 +7684,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>carnosol</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -6731,6 +7721,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>ceanothic acid</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -6763,6 +7758,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>cellobiose</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -6795,6 +7795,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>cerotinic acid</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -6827,6 +7832,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>cholan-24-oic acid, 12-hydroxy-3-oxo-</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -6859,6 +7869,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>cholesterol</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -6891,6 +7906,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>choline</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -6923,6 +7943,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>cinnamic acid</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -6955,6 +7980,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>citramalic acid</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -6987,6 +8017,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>citric acid</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7019,6 +8054,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>citrulline</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7051,6 +8091,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>citrusin VI</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -7083,6 +8128,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>conduritol-beta-epoxide</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -7115,6 +8165,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>creatine</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -7147,6 +8202,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>creatinine</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -7179,6 +8239,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>cysteic acid</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -7211,6 +8276,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>cysteine S-sulfate</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -7243,27 +8313,32 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>cysteine sulfonic acid</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>cytidine (GCMS)</t>
+          <t>cytidine</t>
         </is>
       </c>
       <c r="B216">
-        <v>265.3333333333333</v>
+        <v>642.2222222222222</v>
       </c>
       <c r="C216">
-        <v>445.2777777777778</v>
+        <v>1239.888888888889</v>
       </c>
       <c r="D216">
-        <v>0.06102522471329512</v>
+        <v>0.03598000057262737</v>
       </c>
       <c r="E216">
-        <v>0.7468996837771054</v>
+        <v>0.9490663497871445</v>
       </c>
       <c r="F216">
-        <v>1.214490612704475</v>
+        <v>1.443938834078602</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
@@ -7272,30 +8347,35 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>GCMS</t>
+          <t>LCMS</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>cytidine (LCMS)</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>cytidine (LCMS)</t>
+          <t>cytidine</t>
         </is>
       </c>
       <c r="B217">
-        <v>642.2222222222222</v>
+        <v>265.3333333333333</v>
       </c>
       <c r="C217">
-        <v>1239.888888888889</v>
+        <v>445.2777777777778</v>
       </c>
       <c r="D217">
-        <v>0.03598000057262737</v>
+        <v>0.06102522471329512</v>
       </c>
       <c r="E217">
-        <v>0.9490663497871445</v>
+        <v>0.7468996837771054</v>
       </c>
       <c r="F217">
-        <v>1.443938834078602</v>
+        <v>1.214490612704475</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
@@ -7304,30 +8384,35 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>LCMS</t>
+          <t>GCMS</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>cytidine (GCMS)</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>cytosine (GCMS)</t>
+          <t>cytosine</t>
         </is>
       </c>
       <c r="B218">
-        <v>2311</v>
+        <v>233.3333333333333</v>
       </c>
       <c r="C218">
-        <v>2194.611111111111</v>
+        <v>404</v>
       </c>
       <c r="D218">
-        <v>0.8984477773544919</v>
+        <v>0.03285180636396799</v>
       </c>
       <c r="E218">
-        <v>-0.07455194545623869</v>
+        <v>0.7919628716406221</v>
       </c>
       <c r="F218">
-        <v>0.04650716136625294</v>
+        <v>1.48344074566781</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
@@ -7336,30 +8421,35 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>GCMS</t>
+          <t>LCMS</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>cytosine (LCMS)</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>cytosine (LCMS)</t>
+          <t>cytosine</t>
         </is>
       </c>
       <c r="B219">
-        <v>233.3333333333333</v>
+        <v>2311</v>
       </c>
       <c r="C219">
-        <v>404</v>
+        <v>2194.611111111111</v>
       </c>
       <c r="D219">
-        <v>0.03285180636396799</v>
+        <v>0.8984477773544919</v>
       </c>
       <c r="E219">
-        <v>0.7919628716406221</v>
+        <v>-0.07455194545623869</v>
       </c>
       <c r="F219">
-        <v>1.48344074566781</v>
+        <v>0.04650716136625294</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
@@ -7368,71 +8458,86 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>LCMS</t>
+          <t>GCMS</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>cytosine (GCMS)</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>dehydroabietic acid (GCMS)</t>
+          <t>dehydroabietic acid</t>
         </is>
       </c>
       <c r="B220">
-        <v>6531.833333333333</v>
+        <v>745.7222222222222</v>
       </c>
       <c r="C220">
-        <v>8707.166666666668</v>
+        <v>3835.055555555556</v>
       </c>
       <c r="D220">
-        <v>0.168503885483039</v>
+        <v>0.0153472464202079</v>
       </c>
       <c r="E220">
-        <v>0.4147153592205913</v>
+        <v>2.362537238104656</v>
       </c>
       <c r="F220">
-        <v>0.7733900804045829</v>
+        <v>1.813969533657992</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Not Significant</t>
+          <t>Significant</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>GCMS</t>
+          <t>LCMS</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>dehydroabietic acid (LCMS)</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>dehydroabietic acid (LCMS)</t>
+          <t>dehydroabietic acid</t>
         </is>
       </c>
       <c r="B221">
-        <v>745.7222222222222</v>
+        <v>6531.833333333333</v>
       </c>
       <c r="C221">
-        <v>3835.055555555556</v>
+        <v>8707.166666666668</v>
       </c>
       <c r="D221">
-        <v>0.0153472464202079</v>
+        <v>0.168503885483039</v>
       </c>
       <c r="E221">
-        <v>2.362537238104656</v>
+        <v>0.4147153592205913</v>
       </c>
       <c r="F221">
-        <v>1.813969533657992</v>
+        <v>0.7733900804045829</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Significant</t>
+          <t>Not Significant</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>LCMS</t>
+          <t>GCMS</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>dehydroabietic acid (GCMS)</t>
         </is>
       </c>
     </row>
@@ -7467,6 +8572,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>deoxyguanosine</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -7499,6 +8609,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>deoxypentitol</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -7531,6 +8646,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>dihydrocaffeic acid 3-glucuronide</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -7563,6 +8683,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>dihydrophaseic acid</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -7595,6 +8720,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>dihydroxy-octadecadienoic acid</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -7627,6 +8757,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>dihydroxyacetone</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -7659,6 +8794,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>dimethyldioctadecylammonium</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -7691,6 +8831,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>dodecanedioic acid</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -7723,6 +8868,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>dodecanol</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -7755,6 +8905,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>ectoine</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -7787,6 +8942,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>erythritol</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -7819,6 +8979,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>erythronic acid lactone</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -7851,6 +9016,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>erythrose</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -7883,27 +9053,32 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>ethanolamine</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>ferulic acid (GCMS)</t>
+          <t>ferulic acid</t>
         </is>
       </c>
       <c r="B236">
-        <v>349</v>
+        <v>678.7777777777778</v>
       </c>
       <c r="C236">
-        <v>1291.388888888889</v>
+        <v>2069.722222222222</v>
       </c>
       <c r="D236">
-        <v>0.0003228231801969053</v>
+        <v>0.01127941375120148</v>
       </c>
       <c r="E236">
-        <v>1.887624577754362</v>
+        <v>1.608425917389557</v>
       </c>
       <c r="F236">
-        <v>3.49103528847857</v>
+        <v>1.947713472270643</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
@@ -7912,30 +9087,35 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>GCMS</t>
+          <t>LCMS</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>ferulic acid (LCMS)</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>ferulic acid (LCMS)</t>
+          <t>ferulic acid</t>
         </is>
       </c>
       <c r="B237">
-        <v>678.7777777777778</v>
+        <v>349</v>
       </c>
       <c r="C237">
-        <v>2069.722222222222</v>
+        <v>1291.388888888889</v>
       </c>
       <c r="D237">
-        <v>0.01127941375120148</v>
+        <v>0.0003228231801969053</v>
       </c>
       <c r="E237">
-        <v>1.608425917389557</v>
+        <v>1.887624577754362</v>
       </c>
       <c r="F237">
-        <v>1.947713472270643</v>
+        <v>3.49103528847857</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
@@ -7944,7 +9124,12 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>LCMS</t>
+          <t>GCMS</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>ferulic acid (GCMS)</t>
         </is>
       </c>
     </row>
@@ -7979,68 +9164,83 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>ferulic acid 4-sulfate</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>fructose (GCMS)</t>
+          <t>fructose</t>
         </is>
       </c>
       <c r="B239">
-        <v>42447.5</v>
+        <v>191.9444444444445</v>
       </c>
       <c r="C239">
-        <v>79589.16666666666</v>
+        <v>455.4444444444445</v>
       </c>
       <c r="D239">
-        <v>0.1385355428774918</v>
+        <v>0.02047475947242046</v>
       </c>
       <c r="E239">
-        <v>0.9068924838156458</v>
+        <v>1.246586279359158</v>
       </c>
       <c r="F239">
-        <v>0.8584387890887351</v>
+        <v>1.688781191419271</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Not Significant</t>
+          <t>Significant</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>GCMS</t>
+          <t>LCMS</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>fructose (LCMS)</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>fructose (LCMS)</t>
+          <t>fructose</t>
         </is>
       </c>
       <c r="B240">
-        <v>191.9444444444445</v>
+        <v>42447.5</v>
       </c>
       <c r="C240">
-        <v>455.4444444444445</v>
+        <v>79589.16666666666</v>
       </c>
       <c r="D240">
-        <v>0.02047475947242046</v>
+        <v>0.1385355428774918</v>
       </c>
       <c r="E240">
-        <v>1.246586279359158</v>
+        <v>0.9068924838156458</v>
       </c>
       <c r="F240">
-        <v>1.688781191419271</v>
+        <v>0.8584387890887351</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Significant</t>
+          <t>Not Significant</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>LCMS</t>
+          <t>GCMS</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>fructose (GCMS)</t>
         </is>
       </c>
     </row>
@@ -8075,6 +9275,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>fucose</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -8107,6 +9312,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>fumaric acid</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -8139,6 +9349,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>furfurylmethylamine</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -8171,6 +9386,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>galactinol</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -8203,6 +9423,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>galacto-N-biose</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -8235,6 +9460,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>galactose</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -8267,6 +9497,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>galacturonic acid</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -8299,6 +9534,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>gamma-aminobutyric acid</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -8331,6 +9571,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>glucoheptose</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -8363,68 +9608,83 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>glucoheptulose</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>gluconic acid (GCMS)</t>
+          <t>gluconic acid</t>
         </is>
       </c>
       <c r="B251">
-        <v>29173.11111111111</v>
+        <v>2912.111111111111</v>
       </c>
       <c r="C251">
-        <v>44435.33333333334</v>
+        <v>1006.944444444444</v>
       </c>
       <c r="D251">
-        <v>0.2558939521051933</v>
+        <v>0.004066626098254462</v>
       </c>
       <c r="E251">
-        <v>0.6070680627257788</v>
+        <v>-1.532081313801504</v>
       </c>
       <c r="F251">
-        <v>0.5919399782721739</v>
+        <v>2.390765756518383</v>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Not Significant</t>
+          <t>Significant</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>GCMS</t>
+          <t>LCMS</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>gluconic acid (LCMS)</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>gluconic acid (LCMS)</t>
+          <t>gluconic acid</t>
         </is>
       </c>
       <c r="B252">
-        <v>2912.111111111111</v>
+        <v>29173.11111111111</v>
       </c>
       <c r="C252">
-        <v>1006.944444444444</v>
+        <v>44435.33333333334</v>
       </c>
       <c r="D252">
-        <v>0.004066626098254462</v>
+        <v>0.2558939521051933</v>
       </c>
       <c r="E252">
-        <v>-1.532081313801504</v>
+        <v>0.6070680627257788</v>
       </c>
       <c r="F252">
-        <v>2.390765756518383</v>
+        <v>0.5919399782721739</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Significant</t>
+          <t>Not Significant</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>LCMS</t>
+          <t>GCMS</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>gluconic acid (GCMS)</t>
         </is>
       </c>
     </row>
@@ -8459,27 +9719,32 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>gluconic acid lactone</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>glucose (GCMS)</t>
+          <t>glucose</t>
         </is>
       </c>
       <c r="B254">
-        <v>645153.4444444445</v>
+        <v>7275.944444444443</v>
       </c>
       <c r="C254">
-        <v>508954.3888888889</v>
+        <v>5418.111111111112</v>
       </c>
       <c r="D254">
-        <v>0.01192591613620426</v>
+        <v>0.211816558031792</v>
       </c>
       <c r="E254">
-        <v>-0.3421059628268426</v>
+        <v>-0.4253445476190972</v>
       </c>
       <c r="F254">
-        <v>1.923508248965777</v>
+        <v>0.6740400934222881</v>
       </c>
       <c r="G254" t="inlineStr">
         <is>
@@ -8488,30 +9753,35 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>GCMS</t>
+          <t>LCMS</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>glucose (LCMS)</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>glucose (LCMS)</t>
+          <t>glucose</t>
         </is>
       </c>
       <c r="B255">
-        <v>7275.944444444443</v>
+        <v>645153.4444444445</v>
       </c>
       <c r="C255">
-        <v>5418.111111111112</v>
+        <v>508954.3888888889</v>
       </c>
       <c r="D255">
-        <v>0.211816558031792</v>
+        <v>0.01192591613620426</v>
       </c>
       <c r="E255">
-        <v>-0.4253445476190972</v>
+        <v>-0.3421059628268426</v>
       </c>
       <c r="F255">
-        <v>0.6740400934222881</v>
+        <v>1.923508248965777</v>
       </c>
       <c r="G255" t="inlineStr">
         <is>
@@ -8520,71 +9790,86 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>LCMS</t>
+          <t>GCMS</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>glucose (GCMS)</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>glutamic acid (GCMS)</t>
+          <t>glutamic acid</t>
         </is>
       </c>
       <c r="B256">
-        <v>656184.8888888888</v>
+        <v>4351.333333333334</v>
       </c>
       <c r="C256">
-        <v>374361.6111111111</v>
+        <v>2111</v>
       </c>
       <c r="D256">
-        <v>0.03500191307133009</v>
+        <v>0.02711349823303431</v>
       </c>
       <c r="E256">
-        <v>-0.8096698693601376</v>
+        <v>-1.043530959895721</v>
       </c>
       <c r="F256">
-        <v>1.455908218117823</v>
+        <v>1.566814445337628</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Not Significant</t>
+          <t>Significant</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>GCMS</t>
+          <t>LCMS</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>glutamic acid (LCMS)</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>glutamic acid (LCMS)</t>
+          <t>glutamic acid</t>
         </is>
       </c>
       <c r="B257">
-        <v>4351.333333333334</v>
+        <v>656184.8888888888</v>
       </c>
       <c r="C257">
-        <v>2111</v>
+        <v>374361.6111111111</v>
       </c>
       <c r="D257">
-        <v>0.02711349823303431</v>
+        <v>0.03500191307133009</v>
       </c>
       <c r="E257">
-        <v>-1.043530959895721</v>
+        <v>-0.8096698693601376</v>
       </c>
       <c r="F257">
-        <v>1.566814445337628</v>
+        <v>1.455908218117823</v>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Significant</t>
+          <t>Not Significant</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>LCMS</t>
+          <t>GCMS</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>glutamic acid (GCMS)</t>
         </is>
       </c>
     </row>
@@ -8619,6 +9904,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>glutamine</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -8651,6 +9941,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>glutamyl-valine</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -8683,6 +9978,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>glutaric acid</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -8715,6 +10015,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>glyceric acid</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -8747,6 +10052,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>glycerol</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -8779,6 +10089,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>glycerol-3-galactoside</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -8811,6 +10126,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>glycerol-alpha-phosphate</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -8843,6 +10163,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>glycine</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -8875,6 +10200,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>glycolic acid</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -8907,27 +10237,32 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>glycyl proline</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>guanine (GCMS)</t>
+          <t>guanine</t>
         </is>
       </c>
       <c r="B268">
-        <v>6009.666666666667</v>
+        <v>5843.111111111111</v>
       </c>
       <c r="C268">
-        <v>9813.555555555555</v>
+        <v>9495.833333333332</v>
       </c>
       <c r="D268">
-        <v>0.1642848711282086</v>
+        <v>0.09102167540903772</v>
       </c>
       <c r="E268">
-        <v>0.7074909625623806</v>
+        <v>0.7005578901919218</v>
       </c>
       <c r="F268">
-        <v>0.7844024285798993</v>
+        <v>1.040855174826073</v>
       </c>
       <c r="G268" t="inlineStr">
         <is>
@@ -8936,30 +10271,35 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>GCMS</t>
+          <t>LCMS</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>guanine (LCMS)</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>guanine (LCMS)</t>
+          <t>guanine</t>
         </is>
       </c>
       <c r="B269">
-        <v>5843.111111111111</v>
+        <v>6009.666666666667</v>
       </c>
       <c r="C269">
-        <v>9495.833333333332</v>
+        <v>9813.555555555555</v>
       </c>
       <c r="D269">
-        <v>0.09102167540903772</v>
+        <v>0.1642848711282086</v>
       </c>
       <c r="E269">
-        <v>0.7005578901919218</v>
+        <v>0.7074909625623806</v>
       </c>
       <c r="F269">
-        <v>1.040855174826073</v>
+        <v>0.7844024285798993</v>
       </c>
       <c r="G269" t="inlineStr">
         <is>
@@ -8968,71 +10308,86 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>LCMS</t>
+          <t>GCMS</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>guanine (GCMS)</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>guanosine (GCMS)</t>
+          <t>guanosine</t>
         </is>
       </c>
       <c r="B270">
-        <v>9650.222222222223</v>
+        <v>1338.888888888889</v>
       </c>
       <c r="C270">
-        <v>17678.33333333333</v>
+        <v>2787.944444444444</v>
       </c>
       <c r="D270">
-        <v>0.008995531929633387</v>
+        <v>0.02656233608997873</v>
       </c>
       <c r="E270">
-        <v>0.8733481978603598</v>
+        <v>1.058165572911837</v>
       </c>
       <c r="F270">
-        <v>2.045973150575887</v>
+        <v>1.575733732527962</v>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Not Significant</t>
+          <t>Significant</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>GCMS</t>
+          <t>LCMS</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>guanosine (LCMS)</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>guanosine (LCMS)</t>
+          <t>guanosine</t>
         </is>
       </c>
       <c r="B271">
-        <v>1338.888888888889</v>
+        <v>9650.222222222223</v>
       </c>
       <c r="C271">
-        <v>2787.944444444444</v>
+        <v>17678.33333333333</v>
       </c>
       <c r="D271">
-        <v>0.02656233608997873</v>
+        <v>0.008995531929633387</v>
       </c>
       <c r="E271">
-        <v>1.058165572911837</v>
+        <v>0.8733481978603598</v>
       </c>
       <c r="F271">
-        <v>1.575733732527962</v>
+        <v>2.045973150575887</v>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Significant</t>
+          <t>Not Significant</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>LCMS</t>
+          <t>GCMS</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>guanosine (GCMS)</t>
         </is>
       </c>
     </row>
@@ -9067,6 +10422,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>heptadecanoic acid</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -9099,6 +10459,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>hexadecanedioic acid</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -9131,6 +10496,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>histidine</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -9163,6 +10533,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>homarine</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -9195,6 +10570,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>homocitrulline</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -9227,6 +10607,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>homoserine</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -9259,6 +10644,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>homostachydrine</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -9291,68 +10681,83 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>homovanillic acid</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>hypoxanthine (GCMS)</t>
+          <t>hypoxanthine</t>
         </is>
       </c>
       <c r="B280">
-        <v>8265.277777777777</v>
+        <v>5587.666666666666</v>
       </c>
       <c r="C280">
-        <v>18561.16666666666</v>
+        <v>15510.88888888889</v>
       </c>
       <c r="D280">
-        <v>0.08949379581534907</v>
+        <v>0.01876503157115125</v>
       </c>
       <c r="E280">
-        <v>1.167152183017765</v>
+        <v>1.472963501685242</v>
       </c>
       <c r="F280">
-        <v>1.048207071237753</v>
+        <v>1.726650700573295</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Not Significant</t>
+          <t>Significant</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>GCMS</t>
+          <t>LCMS</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>hypoxanthine (LCMS)</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>hypoxanthine (LCMS)</t>
+          <t>hypoxanthine</t>
         </is>
       </c>
       <c r="B281">
-        <v>5587.666666666666</v>
+        <v>8265.277777777777</v>
       </c>
       <c r="C281">
-        <v>15510.88888888889</v>
+        <v>18561.16666666666</v>
       </c>
       <c r="D281">
-        <v>0.01876503157115125</v>
+        <v>0.08949379581534907</v>
       </c>
       <c r="E281">
-        <v>1.472963501685242</v>
+        <v>1.167152183017765</v>
       </c>
       <c r="F281">
-        <v>1.726650700573295</v>
+        <v>1.048207071237753</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Significant</t>
+          <t>Not Significant</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>LCMS</t>
+          <t>GCMS</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>hypoxanthine (GCMS)</t>
         </is>
       </c>
     </row>
@@ -9387,6 +10792,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>indigotin</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -9419,6 +10829,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>indole-3-acetate</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -9451,6 +10866,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>indole-3-acetyl-glutamine</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -9483,6 +10903,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>indole-3-lactate</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -9515,27 +10940,32 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>indole-6-carboxaldehyde</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>inosine (GCMS)</t>
+          <t>inosine</t>
         </is>
       </c>
       <c r="B287">
-        <v>24822.22222222222</v>
+        <v>4408.777777777777</v>
       </c>
       <c r="C287">
-        <v>28869.16666666666</v>
+        <v>5865.333333333334</v>
       </c>
       <c r="D287">
-        <v>0.2863100931720978</v>
+        <v>0.2663671397515886</v>
       </c>
       <c r="E287">
-        <v>0.2178971842750858</v>
+        <v>0.4118343400571516</v>
       </c>
       <c r="F287">
-        <v>0.5431633417035749</v>
+        <v>0.5745193527179218</v>
       </c>
       <c r="G287" t="inlineStr">
         <is>
@@ -9544,30 +10974,35 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>GCMS</t>
+          <t>LCMS</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>inosine (LCMS)</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>inosine (LCMS)</t>
+          <t>inosine</t>
         </is>
       </c>
       <c r="B288">
-        <v>4408.777777777777</v>
+        <v>24822.22222222222</v>
       </c>
       <c r="C288">
-        <v>5865.333333333334</v>
+        <v>28869.16666666666</v>
       </c>
       <c r="D288">
-        <v>0.2663671397515886</v>
+        <v>0.2863100931720978</v>
       </c>
       <c r="E288">
-        <v>0.4118343400571516</v>
+        <v>0.2178971842750858</v>
       </c>
       <c r="F288">
-        <v>0.5745193527179218</v>
+        <v>0.5431633417035749</v>
       </c>
       <c r="G288" t="inlineStr">
         <is>
@@ -9576,7 +11011,12 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>LCMS</t>
+          <t>GCMS</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>inosine (GCMS)</t>
         </is>
       </c>
     </row>
@@ -9611,6 +11051,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>inositol</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -9643,6 +11088,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>inositol-4-monophosphate</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -9675,27 +11125,32 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>isobutylamine</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>isoleucine (GCMS)</t>
+          <t>isoleucine</t>
         </is>
       </c>
       <c r="B292">
-        <v>548559.7777777778</v>
+        <v>1411.5</v>
       </c>
       <c r="C292">
-        <v>410985</v>
+        <v>1772.944444444444</v>
       </c>
       <c r="D292">
-        <v>0.003183980516742139</v>
+        <v>0.4149170365537732</v>
       </c>
       <c r="E292">
-        <v>-0.4165631030366169</v>
+        <v>0.3289182010303638</v>
       </c>
       <c r="F292">
-        <v>2.497029598439792</v>
+        <v>0.3820387326104275</v>
       </c>
       <c r="G292" t="inlineStr">
         <is>
@@ -9704,30 +11159,35 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>GCMS</t>
+          <t>LCMS</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>isoleucine (LCMS)</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>isoleucine (LCMS)</t>
+          <t>isoleucine</t>
         </is>
       </c>
       <c r="B293">
-        <v>1411.5</v>
+        <v>548559.7777777778</v>
       </c>
       <c r="C293">
-        <v>1772.944444444444</v>
+        <v>410985</v>
       </c>
       <c r="D293">
-        <v>0.4149170365537732</v>
+        <v>0.003183980516742139</v>
       </c>
       <c r="E293">
-        <v>0.3289182010303638</v>
+        <v>-0.4165631030366169</v>
       </c>
       <c r="F293">
-        <v>0.3820387326104275</v>
+        <v>2.497029598439792</v>
       </c>
       <c r="G293" t="inlineStr">
         <is>
@@ -9736,7 +11196,12 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>LCMS</t>
+          <t>GCMS</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>isoleucine (GCMS)</t>
         </is>
       </c>
     </row>
@@ -9771,6 +11236,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>isomaltose</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -9803,6 +11273,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>isothreonic acid</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -9835,6 +11310,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>ketoisoleucine</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -9867,6 +11347,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>lactic acid</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -9899,27 +11384,32 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>lactobionic acid</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>lactose (GCMS)</t>
+          <t>lactose</t>
         </is>
       </c>
       <c r="B299">
-        <v>19716.38888888889</v>
+        <v>210364.3888888889</v>
       </c>
       <c r="C299">
-        <v>36010.05555555555</v>
+        <v>172087.2222222222</v>
       </c>
       <c r="D299">
-        <v>0.003721889905561048</v>
+        <v>0.0829921968540825</v>
       </c>
       <c r="E299">
-        <v>0.869004482962636</v>
+        <v>-0.2897505228600439</v>
       </c>
       <c r="F299">
-        <v>2.429236477555194</v>
+        <v>1.080962739220594</v>
       </c>
       <c r="G299" t="inlineStr">
         <is>
@@ -9928,30 +11418,35 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>GCMS</t>
+          <t>LCMS</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>lactose (LCMS)</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>lactose (LCMS)</t>
+          <t>lactose</t>
         </is>
       </c>
       <c r="B300">
-        <v>210364.3888888889</v>
+        <v>19716.38888888889</v>
       </c>
       <c r="C300">
-        <v>172087.2222222222</v>
+        <v>36010.05555555555</v>
       </c>
       <c r="D300">
-        <v>0.0829921968540825</v>
+        <v>0.003721889905561048</v>
       </c>
       <c r="E300">
-        <v>-0.2897505228600439</v>
+        <v>0.869004482962636</v>
       </c>
       <c r="F300">
-        <v>1.080962739220594</v>
+        <v>2.429236477555194</v>
       </c>
       <c r="G300" t="inlineStr">
         <is>
@@ -9960,7 +11455,12 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>LCMS</t>
+          <t>GCMS</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>lactose (GCMS)</t>
         </is>
       </c>
     </row>
@@ -9995,6 +11495,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>lactulose</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -10027,27 +11532,32 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>laurdan</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>leucine (GCMS)</t>
+          <t>leucine</t>
         </is>
       </c>
       <c r="B303">
-        <v>1019333.333333333</v>
+        <v>4252.277777777777</v>
       </c>
       <c r="C303">
-        <v>714101.2222222222</v>
+        <v>3144.833333333333</v>
       </c>
       <c r="D303">
-        <v>0.0002570182282395098</v>
+        <v>0.3168042496083447</v>
       </c>
       <c r="E303">
-        <v>-0.5134254133785732</v>
+        <v>-0.4352522825799041</v>
       </c>
       <c r="F303">
-        <v>3.590036074555464</v>
+        <v>0.499209001422582</v>
       </c>
       <c r="G303" t="inlineStr">
         <is>
@@ -10056,30 +11566,35 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>GCMS</t>
+          <t>LCMS</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>leucine (LCMS)</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>leucine (LCMS)</t>
+          <t>leucine</t>
         </is>
       </c>
       <c r="B304">
-        <v>4252.277777777777</v>
+        <v>1019333.333333333</v>
       </c>
       <c r="C304">
-        <v>3144.833333333333</v>
+        <v>714101.2222222222</v>
       </c>
       <c r="D304">
-        <v>0.3168042496083447</v>
+        <v>0.0002570182282395098</v>
       </c>
       <c r="E304">
-        <v>-0.4352522825799041</v>
+        <v>-0.5134254133785732</v>
       </c>
       <c r="F304">
-        <v>0.499209001422582</v>
+        <v>3.590036074555464</v>
       </c>
       <c r="G304" t="inlineStr">
         <is>
@@ -10088,7 +11603,12 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>LCMS</t>
+          <t>GCMS</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>leucine (GCMS)</t>
         </is>
       </c>
     </row>
@@ -10123,27 +11643,32 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>leucrose</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>levoglucosan (GCMS)</t>
+          <t>levoglucosan</t>
         </is>
       </c>
       <c r="B306">
-        <v>4697.222222222223</v>
+        <v>3435.777777777778</v>
       </c>
       <c r="C306">
-        <v>4946.944444444444</v>
+        <v>2461.888888888889</v>
       </c>
       <c r="D306">
-        <v>0.7381753924896188</v>
+        <v>0.09420340855650965</v>
       </c>
       <c r="E306">
-        <v>0.07472984964251757</v>
+        <v>-0.4808710766997604</v>
       </c>
       <c r="F306">
-        <v>0.1318404363607587</v>
+        <v>1.025933382870584</v>
       </c>
       <c r="G306" t="inlineStr">
         <is>
@@ -10152,30 +11677,35 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>GCMS</t>
+          <t>LCMS</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>levoglucosan (LCMS)</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>levoglucosan (LCMS)</t>
+          <t>levoglucosan</t>
         </is>
       </c>
       <c r="B307">
-        <v>3435.777777777778</v>
+        <v>4697.222222222223</v>
       </c>
       <c r="C307">
-        <v>2461.888888888889</v>
+        <v>4946.944444444444</v>
       </c>
       <c r="D307">
-        <v>0.09420340855650965</v>
+        <v>0.7381753924896188</v>
       </c>
       <c r="E307">
-        <v>-0.4808710766997604</v>
+        <v>0.07472984964251757</v>
       </c>
       <c r="F307">
-        <v>1.025933382870584</v>
+        <v>0.1318404363607587</v>
       </c>
       <c r="G307" t="inlineStr">
         <is>
@@ -10184,7 +11714,12 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>LCMS</t>
+          <t>GCMS</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>levoglucosan (GCMS)</t>
         </is>
       </c>
     </row>
@@ -10219,6 +11754,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>lignoceric acid</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -10251,6 +11791,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>linoleic acid</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -10283,6 +11828,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>linolenic acid</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -10315,6 +11865,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>lysine</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -10347,6 +11902,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>lyxitol</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -10379,6 +11939,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>lyxose</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -10411,6 +11976,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>malic acid</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -10443,6 +12013,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>malonamide</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -10475,6 +12050,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>malonic acid</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -10507,6 +12087,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>maltitol</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -10539,6 +12124,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>maltose</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -10571,6 +12161,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>maltotetraose</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -10603,6 +12198,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>maltotriitol</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -10635,6 +12235,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>maltotriose</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -10667,27 +12272,32 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>mandelic acid</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>mannitol (GCMS)</t>
+          <t>mannitol</t>
         </is>
       </c>
       <c r="B323">
-        <v>113257.6111111111</v>
+        <v>906.7777777777778</v>
       </c>
       <c r="C323">
-        <v>469774.5</v>
+        <v>5058.944444444443</v>
       </c>
       <c r="D323">
-        <v>1.468307795663842E-05</v>
+        <v>0.001227519957266598</v>
       </c>
       <c r="E323">
-        <v>2.052360398843575</v>
+        <v>2.480015455275853</v>
       </c>
       <c r="F323">
-        <v>4.833182895409999</v>
+        <v>2.910971438300473</v>
       </c>
       <c r="G323" t="inlineStr">
         <is>
@@ -10696,30 +12306,35 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>GCMS</t>
+          <t>LCMS</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>mannitol (LCMS)</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>mannitol (LCMS)</t>
+          <t>mannitol</t>
         </is>
       </c>
       <c r="B324">
-        <v>906.7777777777778</v>
+        <v>113257.6111111111</v>
       </c>
       <c r="C324">
-        <v>5058.944444444443</v>
+        <v>469774.5</v>
       </c>
       <c r="D324">
-        <v>0.001227519957266598</v>
+        <v>1.468307795663842E-05</v>
       </c>
       <c r="E324">
-        <v>2.480015455275853</v>
+        <v>2.052360398843575</v>
       </c>
       <c r="F324">
-        <v>2.910971438300473</v>
+        <v>4.833182895409999</v>
       </c>
       <c r="G324" t="inlineStr">
         <is>
@@ -10728,7 +12343,12 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>LCMS</t>
+          <t>GCMS</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>mannitol (GCMS)</t>
         </is>
       </c>
     </row>
@@ -10763,6 +12383,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>mannoheptulose</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -10795,6 +12420,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>mannonic acid</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -10827,6 +12457,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>mannose-6-phosphate</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -10859,6 +12494,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>mannuronic acid</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -10891,6 +12531,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>methanolphosphate</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -10923,6 +12568,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>methionine</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -10955,6 +12605,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>methionine sulfoxide</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -10987,6 +12642,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>methyl lactoside</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -11019,6 +12679,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>methyl violet B</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -11051,6 +12716,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>methyl-4-hydroxybenzoate</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -11083,6 +12753,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>methylmaleic acid</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -11115,6 +12790,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>mevalonic acid</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -11147,6 +12827,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>montanic acid</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -11179,6 +12864,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>myo-inositol</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -11211,6 +12901,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>myristic acid</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -11243,6 +12938,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>neohesperidose</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -11275,27 +12975,32 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>neomycin B</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>nicotinic acid (GCMS)</t>
+          <t>nicotinic acid</t>
         </is>
       </c>
       <c r="B342">
-        <v>31385</v>
+        <v>1026.055555555556</v>
       </c>
       <c r="C342">
-        <v>33463.55555555555</v>
+        <v>1199.222222222222</v>
       </c>
       <c r="D342">
-        <v>0.6283904815730309</v>
+        <v>0.5838964485939575</v>
       </c>
       <c r="E342">
-        <v>0.09251553322290058</v>
+        <v>0.2249901750785422</v>
       </c>
       <c r="F342">
-        <v>0.2017704019764578</v>
+        <v>0.2336641662296816</v>
       </c>
       <c r="G342" t="inlineStr">
         <is>
@@ -11304,30 +13009,35 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>GCMS</t>
+          <t>LCMS</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>nicotinic acid (LCMS)</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>nicotinic acid (LCMS)</t>
+          <t>nicotinic acid</t>
         </is>
       </c>
       <c r="B343">
-        <v>1026.055555555556</v>
+        <v>31385</v>
       </c>
       <c r="C343">
-        <v>1199.222222222222</v>
+        <v>33463.55555555555</v>
       </c>
       <c r="D343">
-        <v>0.5838964485939575</v>
+        <v>0.6283904815730309</v>
       </c>
       <c r="E343">
-        <v>0.2249901750785422</v>
+        <v>0.09251553322290058</v>
       </c>
       <c r="F343">
-        <v>0.2336641662296816</v>
+        <v>0.2017704019764578</v>
       </c>
       <c r="G343" t="inlineStr">
         <is>
@@ -11336,7 +13046,12 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>LCMS</t>
+          <t>GCMS</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>nicotinic acid (GCMS)</t>
         </is>
       </c>
     </row>
@@ -11371,6 +13086,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>nonadecanoic acid</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -11403,6 +13123,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>norgestrel</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -11435,6 +13160,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>o-toluic acid</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -11467,6 +13197,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>octadecanoic acid, 9,10,18-trihydroxy-</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -11499,6 +13234,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>octadecanol</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -11531,6 +13271,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>oleic acid</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -11563,27 +13308,32 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>ornithine</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>orotic acid (GCMS)</t>
+          <t>orotic acid</t>
         </is>
       </c>
       <c r="B351">
-        <v>304.3888888888889</v>
+        <v>741.0555555555555</v>
       </c>
       <c r="C351">
-        <v>344.4444444444445</v>
+        <v>1753.5</v>
       </c>
       <c r="D351">
-        <v>0.5111885894729137</v>
+        <v>0.05047255949660458</v>
       </c>
       <c r="E351">
-        <v>0.1783556118556202</v>
+        <v>1.242583822730945</v>
       </c>
       <c r="F351">
-        <v>0.291418848872067</v>
+        <v>1.29694467134979</v>
       </c>
       <c r="G351" t="inlineStr">
         <is>
@@ -11592,30 +13342,35 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>GCMS</t>
+          <t>LCMS</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>orotic acid (LCMS)</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>orotic acid (LCMS)</t>
+          <t>orotic acid</t>
         </is>
       </c>
       <c r="B352">
-        <v>741.0555555555555</v>
+        <v>304.3888888888889</v>
       </c>
       <c r="C352">
-        <v>1753.5</v>
+        <v>344.4444444444445</v>
       </c>
       <c r="D352">
-        <v>0.05047255949660458</v>
+        <v>0.5111885894729137</v>
       </c>
       <c r="E352">
-        <v>1.242583822730945</v>
+        <v>0.1783556118556202</v>
       </c>
       <c r="F352">
-        <v>1.29694467134979</v>
+        <v>0.291418848872067</v>
       </c>
       <c r="G352" t="inlineStr">
         <is>
@@ -11624,7 +13379,12 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>LCMS</t>
+          <t>GCMS</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>orotic acid (GCMS)</t>
         </is>
       </c>
     </row>
@@ -11659,6 +13419,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>oxoproline</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -11691,6 +13456,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>p-cresol glucuronide</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -11723,6 +13493,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>p-cresol sulfate</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -11755,6 +13530,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>palatinitol</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -11787,6 +13567,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>palmitoleic acid</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -11819,6 +13604,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>panose</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -11851,6 +13641,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>pantothenic acid</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -11883,6 +13678,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>parabanic acid</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -11915,6 +13715,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>pentaerythritol, cyclic phosphate</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -11947,6 +13752,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>pentamethylene bisacetamide</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -11979,6 +13789,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>pentitol</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -12011,27 +13826,32 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>perfluoroheptanoic acid</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>perseitol (GCMS)</t>
+          <t>perseitol</t>
         </is>
       </c>
       <c r="B365">
-        <v>353.5</v>
+        <v>1427.611111111111</v>
       </c>
       <c r="C365">
-        <v>1644.222222222222</v>
+        <v>5913.111111111112</v>
       </c>
       <c r="D365">
-        <v>0.002441808613255658</v>
+        <v>0.00219020173584539</v>
       </c>
       <c r="E365">
-        <v>2.217623177188575</v>
+        <v>2.050314351460071</v>
       </c>
       <c r="F365">
-        <v>2.612288378664788</v>
+        <v>2.659515881173855</v>
       </c>
       <c r="G365" t="inlineStr">
         <is>
@@ -12040,30 +13860,35 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>GCMS</t>
+          <t>LCMS</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>perseitol (LCMS)</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>perseitol (LCMS)</t>
+          <t>perseitol</t>
         </is>
       </c>
       <c r="B366">
-        <v>1427.611111111111</v>
+        <v>353.5</v>
       </c>
       <c r="C366">
-        <v>5913.111111111112</v>
+        <v>1644.222222222222</v>
       </c>
       <c r="D366">
-        <v>0.00219020173584539</v>
+        <v>0.002441808613255658</v>
       </c>
       <c r="E366">
-        <v>2.050314351460071</v>
+        <v>2.217623177188575</v>
       </c>
       <c r="F366">
-        <v>2.659515881173855</v>
+        <v>2.612288378664788</v>
       </c>
       <c r="G366" t="inlineStr">
         <is>
@@ -12072,7 +13897,12 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>LCMS</t>
+          <t>GCMS</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>perseitol (GCMS)</t>
         </is>
       </c>
     </row>
@@ -12107,6 +13937,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>phenol</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -12139,6 +13974,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>phenyl sulfate</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -12171,27 +14011,32 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>phenylacetic acid</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>phenylalanine (GCMS)</t>
+          <t>phenylalanine</t>
         </is>
       </c>
       <c r="B370">
-        <v>219770.6666666667</v>
+        <v>3727.722222222222</v>
       </c>
       <c r="C370">
-        <v>126682</v>
+        <v>3996.555555555556</v>
       </c>
       <c r="D370">
-        <v>0.0006176546337540702</v>
+        <v>0.7581627934926827</v>
       </c>
       <c r="E370">
-        <v>-0.7947872897719197</v>
+        <v>0.1004627850359466</v>
       </c>
       <c r="F370">
-        <v>3.209254296078226</v>
+        <v>0.1202375321982943</v>
       </c>
       <c r="G370" t="inlineStr">
         <is>
@@ -12200,30 +14045,35 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>GCMS</t>
+          <t>LCMS</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>phenylalanine (LCMS)</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>phenylalanine (LCMS)</t>
+          <t>phenylalanine</t>
         </is>
       </c>
       <c r="B371">
-        <v>3727.722222222222</v>
+        <v>219770.6666666667</v>
       </c>
       <c r="C371">
-        <v>3996.555555555556</v>
+        <v>126682</v>
       </c>
       <c r="D371">
-        <v>0.7581627934926827</v>
+        <v>0.0006176546337540702</v>
       </c>
       <c r="E371">
-        <v>0.1004627850359466</v>
+        <v>-0.7947872897719197</v>
       </c>
       <c r="F371">
-        <v>0.1202375321982943</v>
+        <v>3.209254296078226</v>
       </c>
       <c r="G371" t="inlineStr">
         <is>
@@ -12232,7 +14082,12 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>LCMS</t>
+          <t>GCMS</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>phenylalanine (GCMS)</t>
         </is>
       </c>
     </row>
@@ -12267,6 +14122,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>phenylethylamine</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -12299,68 +14159,83 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>phenylpyruvate</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>phosphate (GCMS)</t>
+          <t>phosphate</t>
         </is>
       </c>
       <c r="B374">
-        <v>43902.66666666666</v>
+        <v>33424.55555555555</v>
       </c>
       <c r="C374">
-        <v>45622.22222222222</v>
+        <v>118534.4444444444</v>
       </c>
       <c r="D374">
-        <v>0.8710850775940236</v>
+        <v>0.0001476196875426892</v>
       </c>
       <c r="E374">
-        <v>0.05542814855841537</v>
+        <v>1.82632606483511</v>
       </c>
       <c r="F374">
-        <v>0.05993942601966702</v>
+        <v>3.830855718251652</v>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Not Significant</t>
+          <t>Significant</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>GCMS</t>
+          <t>LCMS</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>phosphate (LCMS)</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>phosphate (LCMS)</t>
+          <t>phosphate</t>
         </is>
       </c>
       <c r="B375">
-        <v>33424.55555555555</v>
+        <v>43902.66666666666</v>
       </c>
       <c r="C375">
-        <v>118534.4444444444</v>
+        <v>45622.22222222222</v>
       </c>
       <c r="D375">
-        <v>0.0001476196875426892</v>
+        <v>0.8710850775940236</v>
       </c>
       <c r="E375">
-        <v>1.82632606483511</v>
+        <v>0.05542814855841537</v>
       </c>
       <c r="F375">
-        <v>3.830855718251652</v>
+        <v>0.05993942601966702</v>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Significant</t>
+          <t>Not Significant</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>LCMS</t>
+          <t>GCMS</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>phosphate (GCMS)</t>
         </is>
       </c>
     </row>
@@ -12395,6 +14270,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>pimelic acid</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -12427,6 +14307,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>pinitol</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -12459,6 +14344,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>pipecolinic acid</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -12491,6 +14381,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>proline</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -12523,6 +14418,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>proline betaine</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -12555,6 +14455,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>propyleneglycol</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -12587,6 +14492,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>pseudo-uridine</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -12619,6 +14529,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>pseudouridine</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -12651,6 +14566,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>pyroGlu-Val</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -12683,6 +14603,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>pyroglutamic acid</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -12715,6 +14640,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>pyrrole-2-carboxylic acid</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -12747,6 +14677,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>quinic acid</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -12779,6 +14714,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>quinoline-2,8-diol</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -12811,27 +14751,32 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>quinolinic acid</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>raffinose (GCMS)</t>
+          <t>raffinose</t>
         </is>
       </c>
       <c r="B390">
-        <v>16213</v>
+        <v>1369.555555555556</v>
       </c>
       <c r="C390">
-        <v>4348.111111111111</v>
+        <v>1313.055555555556</v>
       </c>
       <c r="D390">
-        <v>0.238297885416807</v>
+        <v>0.8976162139489433</v>
       </c>
       <c r="E390">
-        <v>-1.898690354678993</v>
+        <v>-0.06077983152259761</v>
       </c>
       <c r="F390">
-        <v>0.6228798114340174</v>
+        <v>0.04690931120716751</v>
       </c>
       <c r="G390" t="inlineStr">
         <is>
@@ -12840,30 +14785,35 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>GCMS</t>
+          <t>LCMS</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>raffinose (LCMS)</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>raffinose (LCMS)</t>
+          <t>raffinose</t>
         </is>
       </c>
       <c r="B391">
-        <v>1369.555555555556</v>
+        <v>16213</v>
       </c>
       <c r="C391">
-        <v>1313.055555555556</v>
+        <v>4348.111111111111</v>
       </c>
       <c r="D391">
-        <v>0.8976162139489433</v>
+        <v>0.238297885416807</v>
       </c>
       <c r="E391">
-        <v>-0.06077983152259761</v>
+        <v>-1.898690354678993</v>
       </c>
       <c r="F391">
-        <v>0.04690931120716751</v>
+        <v>0.6228798114340174</v>
       </c>
       <c r="G391" t="inlineStr">
         <is>
@@ -12872,7 +14822,12 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>LCMS</t>
+          <t>GCMS</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>raffinose (GCMS)</t>
         </is>
       </c>
     </row>
@@ -12907,6 +14862,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>ribonic acid</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -12939,6 +14899,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>ribose</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -12971,6 +14936,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>ribulose</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -13003,6 +14973,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>ritalinic acid</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -13035,6 +15010,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>salicyl alcohol</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -13067,6 +15047,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>salicylaldehyde</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -13099,6 +15084,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>salicylic acid</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -13131,6 +15121,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>salicyluric acid</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -13163,27 +15158,32 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>sebacic acid</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>serine (GCMS)</t>
+          <t>serine</t>
         </is>
       </c>
       <c r="B401">
-        <v>318806</v>
+        <v>724.8888888888889</v>
       </c>
       <c r="C401">
-        <v>295256.4444444444</v>
+        <v>782.7777777777777</v>
       </c>
       <c r="D401">
-        <v>0.6374386821265873</v>
+        <v>0.7073831016793971</v>
       </c>
       <c r="E401">
-        <v>-0.1107102323318954</v>
+        <v>0.1108429244851143</v>
       </c>
       <c r="F401">
-        <v>0.195561585474164</v>
+        <v>0.1503453190407012</v>
       </c>
       <c r="G401" t="inlineStr">
         <is>
@@ -13192,30 +15192,35 @@
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>GCMS</t>
+          <t>LCMS</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>serine (LCMS)</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>serine (LCMS)</t>
+          <t>serine</t>
         </is>
       </c>
       <c r="B402">
-        <v>724.8888888888889</v>
+        <v>318806</v>
       </c>
       <c r="C402">
-        <v>782.7777777777777</v>
+        <v>295256.4444444444</v>
       </c>
       <c r="D402">
-        <v>0.7073831016793971</v>
+        <v>0.6374386821265873</v>
       </c>
       <c r="E402">
-        <v>0.1108429244851143</v>
+        <v>-0.1107102323318954</v>
       </c>
       <c r="F402">
-        <v>0.1503453190407012</v>
+        <v>0.195561585474164</v>
       </c>
       <c r="G402" t="inlineStr">
         <is>
@@ -13224,7 +15229,12 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>LCMS</t>
+          <t>GCMS</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>serine (GCMS)</t>
         </is>
       </c>
     </row>
@@ -13259,6 +15269,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>shikimic acid</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -13291,6 +15306,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>sinigrin</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -13323,6 +15343,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>sophorose</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -13355,6 +15380,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>sorbitol</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -13387,6 +15417,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>stearic acid</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -13419,27 +15454,32 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>stigmasterol</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>suberic acid (GCMS)</t>
+          <t>suberic acid</t>
         </is>
       </c>
       <c r="B409">
-        <v>2254.166666666667</v>
+        <v>2785.666666666667</v>
       </c>
       <c r="C409">
-        <v>7868.222222222223</v>
+        <v>10803.11111111111</v>
       </c>
       <c r="D409">
-        <v>0.000790263799007055</v>
+        <v>0.003906228649766897</v>
       </c>
       <c r="E409">
-        <v>1.803443516013626</v>
+        <v>1.955352303452662</v>
       </c>
       <c r="F409">
-        <v>3.102227912090346</v>
+        <v>2.408242339024173</v>
       </c>
       <c r="G409" t="inlineStr">
         <is>
@@ -13448,30 +15488,35 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>GCMS</t>
+          <t>LCMS</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>suberic acid (LCMS)</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>suberic acid (LCMS)</t>
+          <t>suberic acid</t>
         </is>
       </c>
       <c r="B410">
-        <v>2785.666666666667</v>
+        <v>2254.166666666667</v>
       </c>
       <c r="C410">
-        <v>10803.11111111111</v>
+        <v>7868.222222222223</v>
       </c>
       <c r="D410">
-        <v>0.003906228649766897</v>
+        <v>0.000790263799007055</v>
       </c>
       <c r="E410">
-        <v>1.955352303452662</v>
+        <v>1.803443516013626</v>
       </c>
       <c r="F410">
-        <v>2.408242339024173</v>
+        <v>3.102227912090346</v>
       </c>
       <c r="G410" t="inlineStr">
         <is>
@@ -13480,7 +15525,12 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>LCMS</t>
+          <t>GCMS</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>suberic acid (GCMS)</t>
         </is>
       </c>
     </row>
@@ -13515,27 +15565,32 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>succinate semialdehyde</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>succinic acid (GCMS)</t>
+          <t>succinic acid</t>
         </is>
       </c>
       <c r="B412">
-        <v>11341.11111111111</v>
+        <v>4238.611111111111</v>
       </c>
       <c r="C412">
-        <v>14876.55555555555</v>
+        <v>7007.666666666667</v>
       </c>
       <c r="D412">
-        <v>0.04453837603413063</v>
+        <v>0.05099639079920024</v>
       </c>
       <c r="E412">
-        <v>0.3914785397079685</v>
+        <v>0.7253425455199755</v>
       </c>
       <c r="F412">
-        <v>1.351265622332823</v>
+        <v>1.292460559420836</v>
       </c>
       <c r="G412" t="inlineStr">
         <is>
@@ -13544,30 +15599,35 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>GCMS</t>
+          <t>LCMS</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>succinic acid (LCMS)</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>succinic acid (LCMS)</t>
+          <t>succinic acid</t>
         </is>
       </c>
       <c r="B413">
-        <v>4238.611111111111</v>
+        <v>11341.11111111111</v>
       </c>
       <c r="C413">
-        <v>7007.666666666667</v>
+        <v>14876.55555555555</v>
       </c>
       <c r="D413">
-        <v>0.05099639079920024</v>
+        <v>0.04453837603413063</v>
       </c>
       <c r="E413">
-        <v>0.7253425455199755</v>
+        <v>0.3914785397079685</v>
       </c>
       <c r="F413">
-        <v>1.292460559420836</v>
+        <v>1.351265622332823</v>
       </c>
       <c r="G413" t="inlineStr">
         <is>
@@ -13576,30 +15636,35 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>LCMS</t>
+          <t>GCMS</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>succinic acid (GCMS)</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>sucrose (GCMS)</t>
+          <t>sucrose</t>
         </is>
       </c>
       <c r="B414">
-        <v>21083.61111111111</v>
+        <v>96478.72222222222</v>
       </c>
       <c r="C414">
-        <v>10185.94444444445</v>
+        <v>72045.38888888889</v>
       </c>
       <c r="D414">
-        <v>0.1641964820392695</v>
+        <v>0.1406872734583968</v>
       </c>
       <c r="E414">
-        <v>-1.049542233089939</v>
+        <v>-0.4213047033657029</v>
       </c>
       <c r="F414">
-        <v>0.7846361520113394</v>
+        <v>0.8517451869772875</v>
       </c>
       <c r="G414" t="inlineStr">
         <is>
@@ -13608,30 +15673,35 @@
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>GCMS</t>
+          <t>LCMS</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>sucrose (LCMS)</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>sucrose (LCMS)</t>
+          <t>sucrose</t>
         </is>
       </c>
       <c r="B415">
-        <v>96478.72222222222</v>
+        <v>21083.61111111111</v>
       </c>
       <c r="C415">
-        <v>72045.38888888889</v>
+        <v>10185.94444444445</v>
       </c>
       <c r="D415">
-        <v>0.1406872734583968</v>
+        <v>0.1641964820392695</v>
       </c>
       <c r="E415">
-        <v>-0.4213047033657029</v>
+        <v>-1.049542233089939</v>
       </c>
       <c r="F415">
-        <v>0.8517451869772875</v>
+        <v>0.7846361520113394</v>
       </c>
       <c r="G415" t="inlineStr">
         <is>
@@ -13640,7 +15710,12 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>LCMS</t>
+          <t>GCMS</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>sucrose (GCMS)</t>
         </is>
       </c>
     </row>
@@ -13675,6 +15750,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>sulfoacetic acid</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -13707,6 +15787,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>syringa-resinol</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -13739,6 +15824,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>tagatose</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -13771,6 +15861,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>terephthalic acid</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -13803,6 +15898,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>tetracosane</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -13835,6 +15935,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>tetradecane-7-sulfonic acid</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -13867,6 +15972,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>tetradecanedioic acid</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -13899,6 +16009,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>tetradecanedioic acid, 5,6-dihydroxy-</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -13931,6 +16046,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>tetramethyl-4-piperidone</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -13963,6 +16083,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>threitol</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -13995,27 +16120,32 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>threonic acid</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>threonine (GCMS)</t>
+          <t>threonine</t>
         </is>
       </c>
       <c r="B427">
-        <v>75472.88888888889</v>
+        <v>1650.944444444444</v>
       </c>
       <c r="C427">
-        <v>48277.44444444445</v>
+        <v>1030.055555555556</v>
       </c>
       <c r="D427">
-        <v>0.00228759920111963</v>
+        <v>0.08998047188185695</v>
       </c>
       <c r="E427">
-        <v>-0.6446091881738533</v>
+        <v>-0.6805694226891998</v>
       </c>
       <c r="F427">
-        <v>2.640620063790603</v>
+        <v>1.045851733607113</v>
       </c>
       <c r="G427" t="inlineStr">
         <is>
@@ -14024,30 +16154,35 @@
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>GCMS</t>
+          <t>LCMS</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>threonine (LCMS)</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>threonine (LCMS)</t>
+          <t>threonine</t>
         </is>
       </c>
       <c r="B428">
-        <v>1650.944444444444</v>
+        <v>75472.88888888889</v>
       </c>
       <c r="C428">
-        <v>1030.055555555556</v>
+        <v>48277.44444444445</v>
       </c>
       <c r="D428">
-        <v>0.08998047188185695</v>
+        <v>0.00228759920111963</v>
       </c>
       <c r="E428">
-        <v>-0.6805694226891998</v>
+        <v>-0.6446091881738533</v>
       </c>
       <c r="F428">
-        <v>1.045851733607113</v>
+        <v>2.640620063790603</v>
       </c>
       <c r="G428" t="inlineStr">
         <is>
@@ -14056,7 +16191,12 @@
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>LCMS</t>
+          <t>GCMS</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>threonine (GCMS)</t>
         </is>
       </c>
     </row>
@@ -14091,6 +16231,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>threose</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -14123,6 +16268,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>thymidine</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -14155,6 +16305,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>thymine</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -14187,6 +16342,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>trans-4-hydroxyproline</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -14219,6 +16379,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>trehalose</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -14251,6 +16416,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>trehalose-6-phosphate</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -14283,27 +16453,32 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>trimethylamine</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>tryptophan (GCMS)</t>
+          <t>tryptophan</t>
         </is>
       </c>
       <c r="B436">
-        <v>16278.61111111111</v>
+        <v>309.3333333333333</v>
       </c>
       <c r="C436">
-        <v>13703.22222222222</v>
+        <v>416.3333333333334</v>
       </c>
       <c r="D436">
-        <v>0.3584189140617658</v>
+        <v>0.1731398696157622</v>
       </c>
       <c r="E436">
-        <v>-0.2484624410202146</v>
+        <v>0.4285767664803855</v>
       </c>
       <c r="F436">
-        <v>0.4456090803271153</v>
+        <v>0.7616029138672236</v>
       </c>
       <c r="G436" t="inlineStr">
         <is>
@@ -14312,30 +16487,35 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>GCMS</t>
+          <t>LCMS</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>tryptophan (LCMS)</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>tryptophan (LCMS)</t>
+          <t>tryptophan</t>
         </is>
       </c>
       <c r="B437">
-        <v>309.3333333333333</v>
+        <v>16278.61111111111</v>
       </c>
       <c r="C437">
-        <v>416.3333333333334</v>
+        <v>13703.22222222222</v>
       </c>
       <c r="D437">
-        <v>0.1731398696157622</v>
+        <v>0.3584189140617658</v>
       </c>
       <c r="E437">
-        <v>0.4285767664803855</v>
+        <v>-0.2484624410202146</v>
       </c>
       <c r="F437">
-        <v>0.7616029138672236</v>
+        <v>0.4456090803271153</v>
       </c>
       <c r="G437" t="inlineStr">
         <is>
@@ -14344,7 +16524,12 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>LCMS</t>
+          <t>GCMS</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>tryptophan (GCMS)</t>
         </is>
       </c>
     </row>
@@ -14379,68 +16564,83 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>tyramine</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>tyrosine (GCMS)</t>
+          <t>tyrosine</t>
         </is>
       </c>
       <c r="B439">
-        <v>119316.7777777778</v>
+        <v>681.6666666666667</v>
       </c>
       <c r="C439">
-        <v>136357.1111111111</v>
+        <v>2713.444444444444</v>
       </c>
       <c r="D439">
-        <v>0.455715501466758</v>
+        <v>0.007103590331271063</v>
       </c>
       <c r="E439">
-        <v>0.1925930172360999</v>
+        <v>1.992987028535902</v>
       </c>
       <c r="F439">
-        <v>0.3413061983498029</v>
+        <v>2.148522092555832</v>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>Not Significant</t>
+          <t>Significant</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>GCMS</t>
+          <t>LCMS</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>tyrosine (LCMS)</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>tyrosine (LCMS)</t>
+          <t>tyrosine</t>
         </is>
       </c>
       <c r="B440">
-        <v>681.6666666666667</v>
+        <v>119316.7777777778</v>
       </c>
       <c r="C440">
-        <v>2713.444444444444</v>
+        <v>136357.1111111111</v>
       </c>
       <c r="D440">
-        <v>0.007103590331271063</v>
+        <v>0.455715501466758</v>
       </c>
       <c r="E440">
-        <v>1.992987028535902</v>
+        <v>0.1925930172360999</v>
       </c>
       <c r="F440">
-        <v>2.148522092555832</v>
+        <v>0.3413061983498029</v>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>Significant</t>
+          <t>Not Significant</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>LCMS</t>
+          <t>GCMS</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>tyrosine (GCMS)</t>
         </is>
       </c>
     </row>
@@ -14475,27 +16675,32 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>undecanedioic acid</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>uracil (GCMS)</t>
+          <t>uracil</t>
         </is>
       </c>
       <c r="B442">
-        <v>94030.33333333334</v>
+        <v>2359.055555555556</v>
       </c>
       <c r="C442">
-        <v>122367.2777777778</v>
+        <v>4096.166666666666</v>
       </c>
       <c r="D442">
-        <v>0.3461208475573557</v>
+        <v>0.2617597735044113</v>
       </c>
       <c r="E442">
-        <v>0.380019681327539</v>
+        <v>0.7960650232334727</v>
       </c>
       <c r="F442">
-        <v>0.4607722414847063</v>
+        <v>0.5820970937950902</v>
       </c>
       <c r="G442" t="inlineStr">
         <is>
@@ -14504,30 +16709,35 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>GCMS</t>
+          <t>LCMS</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>uracil (LCMS)</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>uracil (LCMS)</t>
+          <t>uracil</t>
         </is>
       </c>
       <c r="B443">
-        <v>2359.055555555556</v>
+        <v>94030.33333333334</v>
       </c>
       <c r="C443">
-        <v>4096.166666666666</v>
+        <v>122367.2777777778</v>
       </c>
       <c r="D443">
-        <v>0.2617597735044113</v>
+        <v>0.3461208475573557</v>
       </c>
       <c r="E443">
-        <v>0.7960650232334727</v>
+        <v>0.380019681327539</v>
       </c>
       <c r="F443">
-        <v>0.5820970937950902</v>
+        <v>0.4607722414847063</v>
       </c>
       <c r="G443" t="inlineStr">
         <is>
@@ -14536,7 +16746,12 @@
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>LCMS</t>
+          <t>GCMS</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>uracil (GCMS)</t>
         </is>
       </c>
     </row>
@@ -14571,68 +16786,83 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>urea</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>uric acid (GCMS)</t>
+          <t>uric acid</t>
         </is>
       </c>
       <c r="B445">
-        <v>842</v>
+        <v>332.3333333333333</v>
       </c>
       <c r="C445">
-        <v>9705.722222222224</v>
+        <v>1299.555555555556</v>
       </c>
       <c r="D445">
-        <v>0.0436403168991967</v>
+        <v>0.07694245449884417</v>
       </c>
       <c r="E445">
-        <v>3.526943432355424</v>
+        <v>1.967315400833086</v>
       </c>
       <c r="F445">
-        <v>1.360112104392753</v>
+        <v>1.113833963619259</v>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>Significant</t>
+          <t>Not Significant</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>GCMS</t>
+          <t>LCMS</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>uric acid (LCMS)</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>uric acid (LCMS)</t>
+          <t>uric acid</t>
         </is>
       </c>
       <c r="B446">
-        <v>332.3333333333333</v>
+        <v>842</v>
       </c>
       <c r="C446">
-        <v>1299.555555555556</v>
+        <v>9705.722222222224</v>
       </c>
       <c r="D446">
-        <v>0.07694245449884417</v>
+        <v>0.0436403168991967</v>
       </c>
       <c r="E446">
-        <v>1.967315400833086</v>
+        <v>3.526943432355424</v>
       </c>
       <c r="F446">
-        <v>1.113833963619259</v>
+        <v>1.360112104392753</v>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>Not Significant</t>
+          <t>Significant</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>LCMS</t>
+          <t>GCMS</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>uric acid (GCMS)</t>
         </is>
       </c>
     </row>
@@ -14667,6 +16897,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>uridine</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -14699,6 +16934,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>urocanic acid</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -14731,6 +16971,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>valine</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -14763,6 +17008,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>valine betaine</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -14795,27 +17045,32 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>vanillic acid</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>xanthine (GCMS)</t>
+          <t>xanthine</t>
         </is>
       </c>
       <c r="B452">
-        <v>1992.055555555555</v>
+        <v>4448.944444444443</v>
       </c>
       <c r="C452">
-        <v>16667.16666666666</v>
+        <v>34727.72222222222</v>
       </c>
       <c r="D452">
-        <v>0.01875066807069255</v>
+        <v>0.01065476848762367</v>
       </c>
       <c r="E452">
-        <v>3.064679086605197</v>
+        <v>2.964552799725701</v>
       </c>
       <c r="F452">
-        <v>1.726983254109781</v>
+        <v>1.972455982424661</v>
       </c>
       <c r="G452" t="inlineStr">
         <is>
@@ -14824,30 +17079,35 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>GCMS</t>
+          <t>LCMS</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>xanthine (LCMS)</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>xanthine (LCMS)</t>
+          <t>xanthine</t>
         </is>
       </c>
       <c r="B453">
-        <v>4448.944444444443</v>
+        <v>1992.055555555555</v>
       </c>
       <c r="C453">
-        <v>34727.72222222222</v>
+        <v>16667.16666666666</v>
       </c>
       <c r="D453">
-        <v>0.01065476848762367</v>
+        <v>0.01875066807069255</v>
       </c>
       <c r="E453">
-        <v>2.964552799725701</v>
+        <v>3.064679086605197</v>
       </c>
       <c r="F453">
-        <v>1.972455982424661</v>
+        <v>1.726983254109781</v>
       </c>
       <c r="G453" t="inlineStr">
         <is>
@@ -14856,7 +17116,12 @@
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>LCMS</t>
+          <t>GCMS</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>xanthine (GCMS)</t>
         </is>
       </c>
     </row>
@@ -14891,6 +17156,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>xanthosine</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -14923,6 +17193,11 @@
           <t>LCMS</t>
         </is>
       </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>xanthurenic acid</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -14955,6 +17230,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>xylitol</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -14987,6 +17267,11 @@
           <t>GCMS</t>
         </is>
       </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>xylose</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -15017,6 +17302,11 @@
       <c r="H458" t="inlineStr">
         <is>
           <t>GCMS</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>xylulose</t>
         </is>
       </c>
     </row>
